--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5504.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5504.xlsx
@@ -2112,6 +2112,12 @@
       <c r="C29" t="n">
         <v>2.08</v>
       </c>
+      <c r="E29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.72</v>
+      </c>
       <c r="G29" t="n">
         <v>1.9</v>
       </c>
@@ -2130,12 +2136,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2166,6 +2172,12 @@
       <c r="C30" t="n">
         <v>2.39</v>
       </c>
+      <c r="E30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.2</v>
+      </c>
       <c r="G30" t="n">
         <v>2.375</v>
       </c>
@@ -2184,12 +2196,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-32-32-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-32-32-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5504.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5504.xlsx
@@ -2112,6 +2112,9 @@
       <c r="C29" t="n">
         <v>2.08</v>
       </c>
+      <c r="D29" t="n">
+        <v>2.562</v>
+      </c>
       <c r="E29" t="n">
         <v>1.72</v>
       </c>
@@ -2131,17 +2134,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, W@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-24-24-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD, W@REF=Y; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2172,6 +2175,9 @@
       <c r="C30" t="n">
         <v>2.39</v>
       </c>
+      <c r="D30" t="n">
+        <v>2.812</v>
+      </c>
       <c r="E30" t="n">
         <v>2.2</v>
       </c>
@@ -2191,17 +2197,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] [BRENNAN-CAD 2026-10-21: N1_1@DRIVE, N1_2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE, W@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-32-32-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5504-32-32-FG (PARTcommunity / CADENAS, N1_1@DRIVE=N, N1_2@DRIVE=N1, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD, W@REF=Y; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
